--- a/N°02 -service et tarifs IN NETWORK.xlsx
+++ b/N°02 -service et tarifs IN NETWORK.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\in_network\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8C37FC-061B-4144-AFF3-08D60396FE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Services principeaux " sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Services secondaires" sheetId="2" r:id="rId6"/>
+    <sheet name="Services principeaux " sheetId="1" r:id="rId1"/>
+    <sheet name="Services secondaires" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>Produit</t>
   </si>
@@ -62,9 +71,6 @@
     <t>Réception, tri et notification aux clients</t>
   </si>
   <si>
-    <t>Acces a l'espace pendant les heures administratives</t>
-  </si>
-  <si>
     <t>Contrat IN Network 1 copie - CGU</t>
   </si>
   <si>
@@ -153,9 +159,6 @@
   </si>
   <si>
     <t>Conseil</t>
-  </si>
-  <si>
-    <t>Workshop de création juridique d'entreprise</t>
   </si>
   <si>
     <t>Casier</t>
@@ -214,17 +217,17 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">Boite aux lettres ® </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>( exculivement pour client domicilié)</t>
     </r>
@@ -234,52 +237,72 @@
   </si>
   <si>
     <t xml:space="preserve">comprise dans la domiciliation </t>
+  </si>
+  <si>
+    <t>formation de création juridique d'entreprise</t>
+  </si>
+  <si>
+    <t>14 chaises, Video projecteur et visio conférences , Tableau blanc et accées internet</t>
+  </si>
+  <si>
+    <t>Externe : 
+J:45 000
+1/2: 25 000</t>
+  </si>
+  <si>
+    <t>Client IN : 
+J: 30 000
+1/2: 15 000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;DZD&quot;* #,##0.00_);_(&quot;DZD&quot;* \(#,##0.00\);_(&quot;DZD&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -289,7 +312,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -323,7 +346,13 @@
     </fill>
   </fills>
   <borders count="30">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -331,20 +360,25 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -354,14 +388,18 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -376,6 +414,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -385,6 +424,8 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -393,19 +434,25 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -415,25 +462,36 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right/>
-    </border>
-    <border>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -442,11 +500,18 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -461,16 +526,21 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -480,15 +550,18 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -503,30 +576,40 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -538,11 +621,17 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -551,14 +640,20 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -567,165 +662,172 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="64">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="5" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -733,7 +835,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -923,23 +1025,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="45.63"/>
-    <col customWidth="1" min="2" max="2" width="44.88"/>
-    <col customWidth="1" min="3" max="3" width="27.5"/>
-    <col customWidth="1" min="4" max="4" width="41.88"/>
+    <col min="1" max="1" width="45.5703125" customWidth="1"/>
+    <col min="2" max="2" width="72.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,314 +1058,313 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15" t="s">
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="50"/>
+      <c r="B3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14"/>
-      <c r="B4" s="20" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="25" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="50"/>
+      <c r="B6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="42"/>
+      <c r="D6" s="54"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="50"/>
+      <c r="B7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="29"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="42"/>
+      <c r="D7" s="54"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
+      <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="29"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="29"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15" t="s">
+      <c r="C8" s="42"/>
+      <c r="D8" s="54"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="54"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="50"/>
+      <c r="B10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="29"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="29"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="32"/>
-      <c r="B11" s="34" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="54"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="52"/>
+      <c r="B11" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="55"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="36"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="41"/>
-      <c r="B13" s="15" t="s">
+      <c r="D12" s="44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="D13" s="45"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="34"/>
+      <c r="B14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="42"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="41"/>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="42"/>
+      <c r="D14" s="45"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="34"/>
+      <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="42"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="41"/>
-      <c r="B15" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="42"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="41"/>
-      <c r="B16" s="15" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="45"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="34"/>
+      <c r="B16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="45"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="34"/>
+      <c r="B17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="42"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="41"/>
-      <c r="B17" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="42"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="43"/>
-      <c r="B18" s="34" t="s">
+      <c r="C17" s="42"/>
+      <c r="D17" s="45"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="35"/>
+      <c r="B18" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="46"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="44"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="41"/>
-      <c r="B20" s="15" t="s">
+      <c r="B19" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="34"/>
+      <c r="B20" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="45"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="34"/>
+      <c r="B21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="42"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="41"/>
-      <c r="B21" s="15" t="s">
+      <c r="C21" s="42"/>
+      <c r="D21" s="45"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="34"/>
+      <c r="B22" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="42"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="41"/>
-      <c r="B22" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="42"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="41"/>
-      <c r="B23" s="15" t="s">
+      <c r="C22" s="42"/>
+      <c r="D22" s="45"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="34"/>
+      <c r="B23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="45"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="34"/>
+      <c r="B24" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="42"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="41"/>
-      <c r="B24" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="42"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="44"/>
-    </row>
-    <row r="26" ht="26.25" customHeight="1">
-      <c r="A26" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="10" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="45"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="35"/>
+      <c r="B25" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="46"/>
+    </row>
+    <row r="26" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="54"/>
-    </row>
-    <row r="27" ht="26.25" customHeight="1">
-      <c r="A27" s="55" t="s">
+      <c r="D26" s="30"/>
+    </row>
+    <row r="27" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="C27" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-    </row>
-    <row r="29" ht="73.5" customHeight="1">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-    </row>
-    <row r="32" ht="88.5" customHeight="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="61" t="s">
+      <c r="D27" s="47" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+    </row>
+    <row r="29" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="38"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+    </row>
+    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+    </row>
+    <row r="32" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+    </row>
+    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="56"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="56"/>
+      <c r="D33" s="31"/>
+    </row>
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C12:C18"/>
+    <mergeCell ref="D12:D18"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="C5:C11"/>
+    <mergeCell ref="D5:D11"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="C19:C25"/>
@@ -1270,228 +1374,230 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="C33:C34"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="C5:C11"/>
-    <mergeCell ref="D5:D11"/>
-    <mergeCell ref="C12:C18"/>
-    <mergeCell ref="D12:D18"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A2:D29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="73.38"/>
-    <col customWidth="1" min="2" max="2" width="53.38"/>
-    <col customWidth="1" min="4" max="4" width="18.38"/>
+    <col min="1" max="1" width="73.42578125" customWidth="1"/>
+    <col min="2" max="2" width="53.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="56" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="60" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="38"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="21"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="21"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="37"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="37"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="37"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="21"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="37"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="21"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="37"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="21"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="37"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="21"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="s">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="38"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="23"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="s">
-        <v>44</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="49">
-        <v>30000.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="53"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="s">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="62"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="29"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="31"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="56"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="56"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="56"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="s">
+      <c r="B25" s="31"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="31"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="31"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="56"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="s">
+      <c r="B28" s="31"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="32" t="s">
         <v>61</v>
-      </c>
-      <c r="B28" s="56"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="60" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1502,6 +1608,6 @@
     <mergeCell ref="D3:D17"/>
     <mergeCell ref="A21:B21"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>